--- a/plantilla_appsheet_panaderia.xlsx
+++ b/plantilla_appsheet_panaderia.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="1" r:id="R356980596b29498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveedores" sheetId="2" r:id="Rb018d2498f464f0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materias_Primas" sheetId="3" r:id="R18ff04e82f5a4217"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos_Terminados" sheetId="4" r:id="Re0d4214079084b80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="5" r:id="Re735139b0d584afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ingresos_MP" sheetId="6" r:id="R19117e78f6874fb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordenes_Produccion" sheetId="7" r:id="R78d55982a8a842c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumos_MP_OP" sheetId="8" r:id="R8e0b9720e8d745f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ventas" sheetId="9" r:id="R6e2b922b350b4fef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle_Ventas" sheetId="10" r:id="Rb6843d60d0184607"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo_Datos" sheetId="11" r:id="Rcf0771f4d0504c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guia_AppSheet" sheetId="12" r:id="R755459f4537f4511"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="13" r:id="R46d54fdec50d40f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="14" r:id="R8f4ad20478874908"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="15" r:id="R734702c3e62b4870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="1" r:id="R2cab62ad0f78486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveedores" sheetId="2" r:id="R5bbdf02676024312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materias_Primas" sheetId="3" r:id="R5be1e12983ff47a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos_Terminados" sheetId="4" r:id="Rf4bfd8470eb04e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="5" r:id="Rc6f74432cac3463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ingresos_MP" sheetId="6" r:id="R20829f0dcb72410a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordenes_Produccion" sheetId="7" r:id="R0fbbcf1ef743436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumos_MP_OP" sheetId="8" r:id="R8fc6d9b7804a4309"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ventas" sheetId="9" r:id="R756e498db5314f00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle_Ventas" sheetId="10" r:id="R8a99107782ec4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo_Datos" sheetId="11" r:id="Rb2f5a611fe2d4b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guia_AppSheet" sheetId="12" r:id="Re13019e883cf4742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="13" r:id="R11a4e544098c49c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="14" r:id="R9c8af937caca46e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="15" r:id="R3be6a0107e1745cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +33,7 @@
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,23 +41,39 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="14"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="1F2937"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1D4ED8"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -66,28 +82,91 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="B45309"/>
+        <x:fgColor rgb="FFB45309"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="7C2D12"/>
+        <x:fgColor rgb="FF7C2D12"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FDE68A"/>
+        <x:fgColor rgb="FFFDE68A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF8A2E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4D35E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD97706"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE0F2FE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7ED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFF6FF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="10">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:left/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:left/>
+    </x:border>
+    <x:border>
+      <x:right/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:bottom/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="50">
+  <x:cellXfs count="150">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -194,6 +273,296 @@
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -201,15 +570,15 @@
   <x:dxfs count="2">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FCA5A5"/>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCA5A5"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FCA5A5"/>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCA5A5"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -718,7 +1087,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c4b6639be6643f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06cb788773674f55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5811,7 +6180,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc94c18d55ee44f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90ceb857f6d9472c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6429,7 +6798,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32b99fe33ef74d34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9651eeb7ad754939"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6438,306 +6807,374 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="64" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="88" t="str">
         <x:v>paso</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>actividad_en_AppSheet</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="B1" s="89" t="str">
+        <x:v>fase</x:v>
+      </x:c>
+      <x:c r="C1" s="89" t="str">
+        <x:v>ruta_editor_actual</x:v>
+      </x:c>
+      <x:c r="D1" s="89" t="str">
         <x:v>configuracion_recomendada</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
-        <x:v>justificacion_academica</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="90" t="str">
         <x:v>resultado_esperado</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="14" t="n">
+    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A2" s="107" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>Preparar el archivo fuente</x:v>
-      </x:c>
-      <x:c r="C2" s="14" t="str">
-        <x:v>Cargar este Excel a Google Drive y, si se desea, convertirlo a Google Sheets antes de crear la app.</x:v>
-      </x:c>
-      <x:c r="D2" s="14" t="str">
-        <x:v>AppSheet trabaja sobre tablas provenientes de hojas de cálculo; una hoja bien normalizada reduce errores de captura y facilita la generación automática del esquema.</x:v>
-      </x:c>
-      <x:c r="E2" s="14" t="str">
-        <x:v>Archivo disponible en Drive como fuente de datos.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="14" t="n">
+      <x:c r="B2" s="108" t="str">
+        <x:v>Preparar la fuente</x:v>
+      </x:c>
+      <x:c r="C2" s="108" t="str">
+        <x:v>Google Drive o OneDrive/SharePoint</x:v>
+      </x:c>
+      <x:c r="D2" s="108" t="str">
+        <x:v>Convertir a Google Sheets para la ruta académica recomendada o conservar .xlsx en una fuente compatible. No usar .xls ni .xlsm.</x:v>
+      </x:c>
+      <x:c r="E2" s="109" t="str">
+        <x:v>Fuente accesible y con encabezados válidos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A3" s="113" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
-        <x:v>Crear la aplicación</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>Ingresar a AppSheet, seleccionar Create/App, elegir la hoja de cálculo y crear la app desde los datos.</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="str">
-        <x:v>El enfoque data-first permite que AppSheet infiera tablas, columnas y formularios iniciales desde el archivo.</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="str">
-        <x:v>Aplicación inicial generada automáticamente.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="14" t="n">
+      <x:c r="B3" s="114" t="str">
+        <x:v>Crear la app</x:v>
+      </x:c>
+      <x:c r="C3" s="114" t="str">
+        <x:v>My Apps &gt; Create &gt; App &gt; Start with existing data</x:v>
+      </x:c>
+      <x:c r="D3" s="114" t="str">
+        <x:v>Elegir la fuente y seleccionar el archivo. Al abrir la pantalla inicial, usar Customize with AppSheet.</x:v>
+      </x:c>
+      <x:c r="E3" s="115" t="str">
+        <x:v>Aplicación inicial generada.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="107" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
-        <x:v>Agregar todas las hojas como tablas</x:v>
-      </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:v>En Data &gt; Tables, verificar o agregar Proveedores, Materias_Primas, Productos_Terminados, Recetas, Ingresos_MP, Ordenes_Produccion, Consumos_MP_OP, Ventas y Detalle_Ventas.</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="str">
-        <x:v>Cada entidad del proceso panadero requiere una tabla; separar entidades evita redundancia y permite integridad referencial.</x:v>
-      </x:c>
-      <x:c r="E4" s="14" t="str">
-        <x:v>Todas las entidades quedan disponibles para formularios, vistas y automatizaciones.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="14" t="n">
+      <x:c r="B4" s="108" t="str">
+        <x:v>Agregar tablas</x:v>
+      </x:c>
+      <x:c r="C4" s="108" t="str">
+        <x:v>Data &gt; +</x:v>
+      </x:c>
+      <x:c r="D4" s="108" t="str">
+        <x:v>Agregar las nueve hojas operativas y revisar Adds, Updates y Deletes.</x:v>
+      </x:c>
+      <x:c r="E4" s="109" t="str">
+        <x:v>Tablas disponibles en el modelo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="113" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>Definir llaves primarias</x:v>
-      </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>En Data &gt; Columns, marcar como Key las columnas id_* de cada tabla y configurar Initial value = UNIQUEID().</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>Una llave primaria identifica cada registro y permite relaciones uno-a-muchos entre tablas.</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>Registros nuevos con identificador único automático.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="14" t="n">
+      <x:c r="B5" s="114" t="str">
+        <x:v>Definir llaves</x:v>
+      </x:c>
+      <x:c r="C5" s="114" t="str">
+        <x:v>Data &gt; tabla &gt; columna</x:v>
+      </x:c>
+      <x:c r="D5" s="114" t="str">
+        <x:v>Marcar id_* como Key, tipo Text, Initial value = UNIQUEID(), no editable y no visible.</x:v>
+      </x:c>
+      <x:c r="E5" s="115" t="str">
+        <x:v>Identificadores estables.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A6" s="107" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>Definir etiquetas visibles</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>Marcar como Label: nombre_proveedor, nombre_materia_prima y nombre_producto.</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>La etiqueta mejora la usabilidad porque el usuario selecciona nombres legibles en vez de códigos internos.</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>Listas desplegables comprensibles para usuarios no técnicos.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="14" t="n">
+      <x:c r="B6" s="108" t="str">
+        <x:v>Definir etiquetas</x:v>
+      </x:c>
+      <x:c r="C6" s="108" t="str">
+        <x:v>Data &gt; tabla &gt; columna</x:v>
+      </x:c>
+      <x:c r="D6" s="108" t="str">
+        <x:v>Marcar nombre_proveedor, nombre_materia_prima y nombre_producto como Label.</x:v>
+      </x:c>
+      <x:c r="E6" s="109" t="str">
+        <x:v>Referencias legibles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="113" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>Configurar relaciones tipo Ref</x:v>
-      </x:c>
-      <x:c r="C7" s="14" t="str">
-        <x:v>Configurar columnas id_producto, id_materia_prima, id_proveedor, id_venta e id_orden_produccion como Ref hacia sus tablas maestras.</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>Las referencias representan claves foráneas y permiten navegación, validación de selección y vistas relacionadas.</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="str">
-        <x:v>La app mostrará vínculos entre proveedores, insumos, producción y ventas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="14" t="n">
+      <x:c r="B7" s="114" t="str">
+        <x:v>Crear referencias</x:v>
+      </x:c>
+      <x:c r="C7" s="114" t="str">
+        <x:v>Data &gt; tabla &gt; columna &gt; Type: Ref</x:v>
+      </x:c>
+      <x:c r="D7" s="114" t="str">
+        <x:v>Configurar las claves foráneas según Modelo_Datos.</x:v>
+      </x:c>
+      <x:c r="E7" s="115" t="str">
+        <x:v>Integridad referencial y navegación.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="107" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>Configurar formularios de captura</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>Crear o ajustar formularios para Proveedores, Materias_Primas, Productos_Terminados, Ingresos_MP, Ordenes_Produccion, Consumos_MP_OP, Ventas y Detalle_Ventas.</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="str">
-        <x:v>Los formularios son el mecanismo de captura controlada; permiten requeridos, listas, tipos de dato y validaciones.</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="str">
-        <x:v>Usuarios pueden registrar datos operativos desde móvil o web.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="14" t="n">
+      <x:c r="B8" s="108" t="str">
+        <x:v>Configurar padre-hijo</x:v>
+      </x:c>
+      <x:c r="C8" s="108" t="str">
+        <x:v>Data &gt; columna Ref &gt; IsPartOf</x:v>
+      </x:c>
+      <x:c r="D8" s="108" t="str">
+        <x:v>Activar en Detalle_Ventas[id_venta] y Consumos_MP_OP[id_orden_produccion].</x:v>
+      </x:c>
+      <x:c r="E8" s="109" t="str">
+        <x:v>Detalles integrados en el formulario padre.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A9" s="113" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>Configurar ingreso de materia prima</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>En Ingresos_MP, usar fecha_ingreso como Date, cantidad como Decimal, costo_unitario como Price, id_materia_prima y id_proveedor como Ref.</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="str">
-        <x:v>El ingreso de materia prima debe tener trazabilidad de fecha, proveedor, lote, vencimiento, cantidad y costo para control de inventario y calidad.</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="str">
-        <x:v>Entradas de inventario documentadas y consultables.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="14" t="n">
+      <x:c r="B9" s="114" t="str">
+        <x:v>Revisar tipos</x:v>
+      </x:c>
+      <x:c r="C9" s="114" t="str">
+        <x:v>Data &gt; tabla &gt; columnas</x:v>
+      </x:c>
+      <x:c r="D9" s="114" t="str">
+        <x:v>Usar Date, DateTime, Decimal, Price, Email, Phone, LongText, Enum y Ref según corresponda.</x:v>
+      </x:c>
+      <x:c r="E9" s="115" t="str">
+        <x:v>Captura coherente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A10" s="107" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="14" t="str">
-        <x:v>Configurar recetas</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="str">
-        <x:v>En Recetas, asociar cada producto terminado con las materias primas requeridas y la cantidad por unidad.</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="str">
-        <x:v>La receta opera como lista de materiales: define estándares de consumo para planear producción y controlar desviaciones.</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="str">
-        <x:v>Base técnica para calcular necesidades de materia prima.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="14" t="n">
+      <x:c r="B10" s="108" t="str">
+        <x:v>Configurar listas</x:v>
+      </x:c>
+      <x:c r="C10" s="108" t="str">
+        <x:v>Data &gt; columna Enum</x:v>
+      </x:c>
+      <x:c r="D10" s="108" t="str">
+        <x:v>Definir estados, unidades, categorías y medios de pago como opciones controladas.</x:v>
+      </x:c>
+      <x:c r="E10" s="109" t="str">
+        <x:v>Valores normalizados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="113" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="14" t="str">
-        <x:v>Configurar orden de producción</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="str">
-        <x:v>En Ordenes_Produccion, seleccionar producto, cantidad planificada, cantidad producida y estado_orden.</x:v>
-      </x:c>
-      <x:c r="D11" s="14" t="str">
-        <x:v>La orden de producción conecta la demanda de producción con el consumo real y la generación de inventario de producto terminado.</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="str">
-        <x:v>Órdenes planificadas, en proceso, cerradas o canceladas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="14" t="n">
+      <x:c r="B11" s="114" t="str">
+        <x:v>Calcular costos</x:v>
+      </x:c>
+      <x:c r="C11" s="114" t="str">
+        <x:v>Data &gt; columna &gt; App formula</x:v>
+      </x:c>
+      <x:c r="D11" s="114" t="str">
+        <x:v>Configurar costo_total y costo_total_consumo.</x:v>
+      </x:c>
+      <x:c r="E11" s="115" t="str">
+        <x:v>Costos calculados automáticamente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A12" s="107" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="14" t="str">
-        <x:v>Registrar consumo real de materia prima</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="str">
-        <x:v>En Consumos_MP_OP, capturar insumos efectivamente consumidos por orden de producción.</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="str">
-        <x:v>El control real permite comparar estándar versus ejecución y soporta trazabilidad del inventario.</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="str">
-        <x:v>Descuento de materia prima asociado a cada orden.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="14" t="n">
+      <x:c r="B12" s="108" t="str">
+        <x:v>Configurar ventas</x:v>
+      </x:c>
+      <x:c r="C12" s="108" t="str">
+        <x:v>Data &gt; Detalle_Ventas</x:v>
+      </x:c>
+      <x:c r="D12" s="108" t="str">
+        <x:v>Usar precio_unitario como Initial value, subtotal como App formula y total_venta como columna virtual.</x:v>
+      </x:c>
+      <x:c r="E12" s="109" t="str">
+        <x:v>Venta totalizable con precio histórico.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A13" s="113" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B13" s="14" t="str">
-        <x:v>Configurar ventas con detalle</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="str">
-        <x:v>En Ventas registrar encabezado; en Detalle_Ventas registrar productos, cantidades, precio unitario y subtotal.</x:v>
-      </x:c>
-      <x:c r="D13" s="14" t="str">
-        <x:v>Separar encabezado y detalle permite una venta con varios productos y evita duplicar información de cliente, fecha y medio de pago.</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="str">
-        <x:v>Ventas trazables y totalizables por producto, fecha y medio de pago.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="14" t="n">
+      <x:c r="B13" s="114" t="str">
+        <x:v>Calcular inventarios</x:v>
+      </x:c>
+      <x:c r="C13" s="114" t="str">
+        <x:v>Data &gt; Materias_Primas / Productos_Terminados</x:v>
+      </x:c>
+      <x:c r="D13" s="114" t="str">
+        <x:v>Crear stock_actual_mp y stock_actual_producto como columnas virtuales con las expresiones del Modelo_Datos.</x:v>
+      </x:c>
+      <x:c r="E13" s="115" t="str">
+        <x:v>Inventarios estimados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A14" s="107" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="14" t="str">
-        <x:v>Crear columnas virtuales de inventario</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="str">
-        <x:v>Crear stock_actual_mp y stock_actual_producto con las expresiones del sheet Modelo_Datos.</x:v>
-      </x:c>
-      <x:c r="D14" s="14" t="str">
-        <x:v>Las existencias deben calcularse a partir de transacciones, no editarse manualmente, para preservar consistencia contable-operativa.</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="str">
-        <x:v>Inventario actualizado por entradas, producción, consumo y ventas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="14" t="n">
+      <x:c r="B14" s="108" t="str">
+        <x:v>Agregar validaciones</x:v>
+      </x:c>
+      <x:c r="C14" s="108" t="str">
+        <x:v>Data &gt; columna &gt; Valid_If</x:v>
+      </x:c>
+      <x:c r="D14" s="108" t="str">
+        <x:v>Impedir cantidades inválidas y fechas de vencimiento anteriores al ingreso.</x:v>
+      </x:c>
+      <x:c r="E14" s="109" t="str">
+        <x:v>Datos consistentes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="113" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B15" s="14" t="str">
-        <x:v>Crear vistas principales</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="str">
-        <x:v>Crear vistas tipo Deck/Table/Form: Materias primas, Productos, Producción, Ventas y Proveedores.</x:v>
-      </x:c>
-      <x:c r="D15" s="14" t="str">
-        <x:v>La experiencia de usuario debe reflejar los procesos críticos de la panadería y no solo la estructura de la base de datos.</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="str">
-        <x:v>Menú operativo claro para la primera versión.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="14" t="n">
+      <x:c r="B15" s="114" t="str">
+        <x:v>Ordenar formularios</x:v>
+      </x:c>
+      <x:c r="C15" s="114" t="str">
+        <x:v>App &gt; Views &gt; Form</x:v>
+      </x:c>
+      <x:c r="D15" s="114" t="str">
+        <x:v>Organizar campos y dejar los identificadores técnicos ocultos.</x:v>
+      </x:c>
+      <x:c r="E15" s="115" t="str">
+        <x:v>Formularios claros.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="107" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="14" t="str">
-        <x:v>Probar la primera versión</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="str">
-        <x:v>Ejecutar el flujo mínimo: crear proveedor, crear materia prima, registrar ingreso, crear producto, definir receta, crear orden, registrar consumo, registrar venta.</x:v>
-      </x:c>
-      <x:c r="D16" s="14" t="str">
-        <x:v>La prueba de extremo a extremo valida coherencia del modelo, formularios, referencias y cálculos.</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="str">
-        <x:v>MVP funcional para control básico de producción y ventas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="14" t="n">
+      <x:c r="B16" s="108" t="str">
+        <x:v>Crear vistas</x:v>
+      </x:c>
+      <x:c r="C16" s="108" t="str">
+        <x:v>App &gt; Views</x:v>
+      </x:c>
+      <x:c r="D16" s="108" t="str">
+        <x:v>Configurar Table, Deck, Detail y Form para los procesos principales.</x:v>
+      </x:c>
+      <x:c r="E16" s="109" t="str">
+        <x:v>Navegación operativa.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="113" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B17" s="14" t="str">
-        <x:v>Ajustar seguridad y despliegue</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="str">
-        <x:v>Definir usuarios autorizados, permisos de edición por tabla y sincronización antes de publicar.</x:v>
-      </x:c>
-      <x:c r="D17" s="14" t="str">
-        <x:v>Una app operativa necesita controlar quién puede crear, editar o consultar información sensible.</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="str">
-        <x:v>Aplicación lista para piloto controlado en la panadería.</x:v>
+      <x:c r="B17" s="114" t="str">
+        <x:v>Crear tablero</x:v>
+      </x:c>
+      <x:c r="C17" s="114" t="str">
+        <x:v>App &gt; Views &gt; Dashboard</x:v>
+      </x:c>
+      <x:c r="D17" s="114" t="str">
+        <x:v>Combinar inventario bajo, órdenes por estado y ventas recientes.</x:v>
+      </x:c>
+      <x:c r="E17" s="115" t="str">
+        <x:v>Resumen visual.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A18" s="119" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="120" t="str">
+        <x:v>Configurar seguridad</x:v>
+      </x:c>
+      <x:c r="C18" s="120" t="str">
+        <x:v>Security &gt; Require sign-in</x:v>
+      </x:c>
+      <x:c r="D18" s="120" t="str">
+        <x:v>Exigir inicio de sesión para el piloto y compartir solo con usuarios autorizados.</x:v>
+      </x:c>
+      <x:c r="E18" s="121" t="str">
+        <x:v>Acceso controlado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A19" s="125" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="126" t="str">
+        <x:v>Revisar sincronización</x:v>
+      </x:c>
+      <x:c r="C19" s="126" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="D19" s="126" t="str">
+        <x:v>Configurar localización, rendimiento, sincronización y uso sin conexión solo si se prueba.</x:v>
+      </x:c>
+      <x:c r="E19" s="127" t="str">
+        <x:v>Comportamiento estable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A20" s="119" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="120" t="str">
+        <x:v>Probar</x:v>
+      </x:c>
+      <x:c r="C20" s="120" t="str">
+        <x:v>Vista previa activa</x:v>
+      </x:c>
+      <x:c r="D20" s="120" t="str">
+        <x:v>Ejecutar el flujo proveedor &gt; ingreso &gt; producción &gt; consumo &gt; venta y verificar cálculos.</x:v>
+      </x:c>
+      <x:c r="E20" s="121" t="str">
+        <x:v>Prueba integral satisfactoria.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="131" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="132" t="str">
+        <x:v>Desplegar</x:v>
+      </x:c>
+      <x:c r="C21" s="132" t="str">
+        <x:v>Manage &gt; Deploy &gt; Deployment Check</x:v>
+      </x:c>
+      <x:c r="D21" s="132" t="str">
+        <x:v>Corregir errores y advertencias antes de publicar o sustentar.</x:v>
+      </x:c>
+      <x:c r="E21" s="133" t="str">
+        <x:v>Aplicación validada para piloto.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R868d00a9e52c49e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f127412c86d46d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6746,114 +7183,180 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="80" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="88" t="str">
         <x:v>tema</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>fuente_URL</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
-        <x:v>uso_en_el_diseno</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="14" t="str">
-        <x:v>Diseño general de apps en AppSheet</x:v>
-      </x:c>
-      <x:c r="B2" s="14" t="str">
+      <x:c r="B1" s="89" t="str">
+        <x:v>fuente_oficial</x:v>
+      </x:c>
+      <x:c r="C1" s="90" t="str">
+        <x:v>uso_en_el_taller</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A2" s="137" t="str">
+        <x:v>Editor vigente</x:v>
+      </x:c>
+      <x:c r="B2" s="138" t="str">
+        <x:v>https://support.google.com/appsheet/answer/12290157?hl=en</x:v>
+      </x:c>
+      <x:c r="C2" s="139" t="str">
+        <x:v>Navegación actual: Data, App, Actions, Automation, Security, Settings y Manage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A3" s="113" t="str">
+        <x:v>Mejoras del editor</x:v>
+      </x:c>
+      <x:c r="B3" s="114" t="str">
+        <x:v>https://support.google.com/appsheet/answer/12490168?hl=en</x:v>
+      </x:c>
+      <x:c r="C3" s="115" t="str">
+        <x:v>Confirma que el editor mejorado es el predeterminado y documenta equivalencias con el editor heredado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A4" s="137" t="str">
+        <x:v>Crear app desde datos</x:v>
+      </x:c>
+      <x:c r="B4" s="138" t="str">
+        <x:v>https://support.google.com/appsheet/answer/12008053?hl=en</x:v>
+      </x:c>
+      <x:c r="C4" s="139" t="str">
+        <x:v>Ruta My Apps &gt; Create &gt; App &gt; Start with existing data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A5" s="113" t="str">
+        <x:v>Excel como fuente</x:v>
+      </x:c>
+      <x:c r="B5" s="114" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10106311?hl=en</x:v>
+      </x:c>
+      <x:c r="C5" s="115" t="str">
+        <x:v>Compatibilidad con .xlsx y restricciones para .xls y .xlsm.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A6" s="137" t="str">
+        <x:v>Llaves</x:v>
+      </x:c>
+      <x:c r="B6" s="138" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10106672?hl=en</x:v>
+      </x:c>
+      <x:c r="C6" s="139" t="str">
+        <x:v>Criterios para identificar filas de forma única.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A7" s="113" t="str">
+        <x:v>UNIQUEID()</x:v>
+      </x:c>
+      <x:c r="B7" s="114" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10108209?hl=en</x:v>
+      </x:c>
+      <x:c r="C7" s="115" t="str">
+        <x:v>Generación de identificadores estables.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A8" s="137" t="str">
+        <x:v>Referencias</x:v>
+      </x:c>
+      <x:c r="B8" s="138" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10106510?hl=en</x:v>
+      </x:c>
+      <x:c r="C8" s="139" t="str">
+        <x:v>Relaciones entre tablas mediante columnas Ref.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A9" s="113" t="str">
+        <x:v>Columnas virtuales</x:v>
+      </x:c>
+      <x:c r="B9" s="114" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10106758?hl=en</x:v>
+      </x:c>
+      <x:c r="C9" s="115" t="str">
+        <x:v>Cálculos no almacenados físicamente en la fuente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A10" s="144" t="str">
+        <x:v>Valid_If</x:v>
+      </x:c>
+      <x:c r="B10" s="145" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10107949?hl=en</x:v>
+      </x:c>
+      <x:c r="C10" s="146" t="str">
+        <x:v>Validación de valores capturados en formularios.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A11" s="125" t="str">
+        <x:v>Diseño de vistas</x:v>
+      </x:c>
+      <x:c r="B11" s="126" t="str">
         <x:v>https://support.google.com/appsheet/answer/10099795?hl=en</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str">
-        <x:v>Proceso general: definir entidades, construir la hoja, conectar los datos, refinar UX, comportamiento y seguridad.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="14" t="str">
-        <x:v>Uso de hojas de cálculo como fuente</x:v>
-      </x:c>
-      <x:c r="B3" s="14" t="str">
-        <x:v>https://support.google.com/appsheet/answer/10099320?hl=en</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>Sustenta el uso de un archivo Excel/Google Sheets con varias hojas como fuente de tablas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="14" t="str">
-        <x:v>Uso de múltiples hojas como tablas</x:v>
-      </x:c>
-      <x:c r="B4" s="14" t="str">
-        <x:v>https://support.google.com/appsheet/answer/10106507?hl=en</x:v>
-      </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:v>Sustenta que varias hojas de un mismo archivo pueden agregarse como tablas de AppSheet.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>Columnas y esquema</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>https://support.google.com/appsheet/answer/10106509?hl=en</x:v>
-      </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Sustenta la revisión y regeneración de columnas cuando cambia la estructura de datos.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="14" t="str">
-        <x:v>Referencias entre tablas</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>https://support.google.com/appsheet/answer/10106510?hl=en</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>Sustenta el uso de columnas Ref para relacionar tablas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>Tipos de dato</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>https://support.google.com/appsheet/answer/10106435?hl=en</x:v>
-      </x:c>
-      <x:c r="C7" s="14" t="str">
-        <x:v>Sustenta tipos de dato como Ref, Date, Price, Number y Yes/No.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>Expresiones, fórmulas e Initial Value</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>https://support.google.com/appsheet/answer/10106437?hl=en</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>Sustenta el uso de App formulas e Initial values para cálculos y llaves automáticas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>Expresiones en AppSheet</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>https://support.google.com/appsheet/answer/10104642?hl=en</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>Sustenta el uso de expresiones en columnas virtuales, restricciones y valores iniciales.</x:v>
+      <x:c r="C11" s="127" t="str">
+        <x:v>Tipos de vista y navegación.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A12" s="144" t="str">
+        <x:v>Regenerar esquema</x:v>
+      </x:c>
+      <x:c r="B12" s="145" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10106675?hl=en</x:v>
+      </x:c>
+      <x:c r="C12" s="146" t="str">
+        <x:v>Actualización del modelo después de cambiar columnas en la fuente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A13" s="125" t="str">
+        <x:v>Seguridad</x:v>
+      </x:c>
+      <x:c r="B13" s="126" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10105078?hl=en</x:v>
+      </x:c>
+      <x:c r="C13" s="127" t="str">
+        <x:v>Inicio de sesión, usuarios y filtros de seguridad.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A14" s="144" t="str">
+        <x:v>Despliegue</x:v>
+      </x:c>
+      <x:c r="B14" s="145" t="str">
+        <x:v>https://support.google.com/appsheet/answer/10104495?hl=en</x:v>
+      </x:c>
+      <x:c r="C14" s="146" t="str">
+        <x:v>Deployment Check y publicación.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A15" s="131" t="str">
+        <x:v>Notas de versión</x:v>
+      </x:c>
+      <x:c r="B15" s="132" t="str">
+        <x:v>https://discuss.google.dev/c/appsheet/appsheet-release-notes/123</x:v>
+      </x:c>
+      <x:c r="C15" s="133" t="str">
+        <x:v>Seguimiento de cambios recientes de la plataforma.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R663cad44b059493f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98ecd561ac6f46d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6987,73 +7490,188 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="90" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="35" t="str">
-        <x:v>Plantilla de datos para AppSheet - Panadería</x:v>
-      </x:c>
-      <x:c r="B1" s="35" t="str">
-        <x:v>Plantilla de datos para AppSheet - Panadería</x:v>
-      </x:c>
-      <x:c r="C1" s="35" t="str">
-        <x:v>Plantilla de datos para AppSheet - Panadería</x:v>
-      </x:c>
-      <x:c r="D1" s="35" t="str">
-        <x:v>Plantilla de datos para AppSheet - Panadería</x:v>
-      </x:c>
-      <x:c r="E1" s="35" t="str">
-        <x:v>Plantilla de datos para AppSheet - Panadería</x:v>
-      </x:c>
-      <x:c r="F1" s="35" t="str">
-        <x:v>Plantilla de datos para AppSheet - Panadería</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="44" t="str">
-        <x:v>Propósito</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="str">
-        <x:v>Diseñar una primera versión de una app para controlar materia prima, proveedores, productos terminados, órdenes de producción y ventas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="44" t="str">
+    <x:row r="1" ht="28" hidden="0" customHeight="1">
+      <x:c r="A1" s="70" t="str">
+        <x:v>Taller AppSheet - Gestión básica de una panadería</x:v>
+      </x:c>
+      <x:c r="B1" s="71"/>
+      <x:c r="C1" s="71"/>
+      <x:c r="D1" s="71"/>
+      <x:c r="E1" s="71"/>
+      <x:c r="F1" s="72"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="73"/>
+      <x:c r="B2" s="74"/>
+      <x:c r="C2" s="74"/>
+      <x:c r="D2" s="74"/>
+      <x:c r="E2" s="74"/>
+      <x:c r="F2" s="75"/>
+    </x:row>
+    <x:row r="3" ht="34" hidden="0" customHeight="1">
+      <x:c r="A3" s="76" t="str">
+        <x:v>Objetivo del taller</x:v>
+      </x:c>
+      <x:c r="B3" s="77" t="str">
+        <x:v>Construir y validar una primera versión funcional de una aplicación en AppSheet para gestionar proveedores, materias primas, productos terminados, recetas, ingresos de insumos, órdenes de producción, consumos y ventas; configurar llaves, referencias, formularios, validaciones, cálculos de inventario estimado y vistas de consulta; y ejecutar una prueba integral desde el ingreso de materia prima hasta la venta del producto terminado.</x:v>
+      </x:c>
+      <x:c r="C3" s="77"/>
+      <x:c r="D3" s="77"/>
+      <x:c r="E3" s="77"/>
+      <x:c r="F3" s="78"/>
+    </x:row>
+    <x:row r="4" ht="34" hidden="0" customHeight="1">
+      <x:c r="A4" s="76"/>
+      <x:c r="B4" s="77"/>
+      <x:c r="C4" s="77"/>
+      <x:c r="D4" s="77"/>
+      <x:c r="E4" s="77"/>
+      <x:c r="F4" s="78"/>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="79"/>
+      <x:c r="B5" s="77"/>
+      <x:c r="C5" s="77"/>
+      <x:c r="D5" s="77"/>
+      <x:c r="E5" s="77"/>
+      <x:c r="F5" s="78"/>
+    </x:row>
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A6" s="80" t="str">
+        <x:v>Recursos del taller — mantener todos los archivos en la misma carpeta</x:v>
+      </x:c>
+      <x:c r="B6" s="81"/>
+      <x:c r="C6" s="81"/>
+      <x:c r="D6" s="81"/>
+      <x:c r="E6" s="81"/>
+      <x:c r="F6" s="82"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="76" t="str">
+        <x:v>README principal</x:v>
+      </x:c>
+      <x:c r="B7" s="149" t="str">
+        <x:v>README.md</x:v>
+      </x:c>
+      <x:c r="C7" s="77"/>
+      <x:c r="D7" s="77"/>
+      <x:c r="E7" s="77"/>
+      <x:c r="F7" s="78"/>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="83" t="str">
+        <x:v>1. Conceptos Básicos de AppSheet</x:v>
+      </x:c>
+      <x:c r="B8" s="149" t="str">
+        <x:v>1_Conceptos_Basicos_de_AppSheet.md</x:v>
+      </x:c>
+      <x:c r="C8" s="77"/>
+      <x:c r="D8" s="77"/>
+      <x:c r="E8" s="77"/>
+      <x:c r="F8" s="78"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="83" t="str">
+        <x:v>2. Contexto del taller</x:v>
+      </x:c>
+      <x:c r="B9" s="149" t="str">
+        <x:v>2_Contexto_del_taller.md</x:v>
+      </x:c>
+      <x:c r="C9" s="77"/>
+      <x:c r="D9" s="77"/>
+      <x:c r="E9" s="77"/>
+      <x:c r="F9" s="78"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="83" t="str">
+        <x:v>3. Guía paso a paso</x:v>
+      </x:c>
+      <x:c r="B10" s="149" t="str">
+        <x:v>3_Guia_paso_a_paso.md</x:v>
+      </x:c>
+      <x:c r="C10" s="77"/>
+      <x:c r="D10" s="77"/>
+      <x:c r="E10" s="77"/>
+      <x:c r="F10" s="78"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="73"/>
+      <x:c r="B11" s="77"/>
+      <x:c r="C11" s="77"/>
+      <x:c r="D11" s="77"/>
+      <x:c r="E11" s="77"/>
+      <x:c r="F11" s="78"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="83" t="str">
+        <x:v>Vigencia</x:v>
+      </x:c>
+      <x:c r="B12" s="77" t="str">
+        <x:v>Material revisado el 17 de junio de 2026 con el editor mejorado de AppSheet, habilitado de forma predeterminada.</x:v>
+      </x:c>
+      <x:c r="C12" s="77"/>
+      <x:c r="D12" s="77"/>
+      <x:c r="E12" s="77"/>
+      <x:c r="F12" s="78"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="83" t="str">
+        <x:v>Navegación actual</x:v>
+      </x:c>
+      <x:c r="B13" s="77" t="str">
+        <x:v>Data, App, Actions, Automation, Security, Settings y Manage. UX y Behavior corresponden al editor heredado.</x:v>
+      </x:c>
+      <x:c r="C13" s="77"/>
+      <x:c r="D13" s="77"/>
+      <x:c r="E13" s="77"/>
+      <x:c r="F13" s="78"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="83" t="str">
         <x:v>Uso recomendado</x:v>
       </x:c>
-      <x:c r="B4" s="12" t="str">
-        <x:v>Subir el archivo a Google Drive, crear la app en AppSheet, agregar cada hoja operativa como tabla y configurar llaves, referencias, formularios y vistas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="44" t="str">
-        <x:v>Hojas operativas para AppSheet</x:v>
-      </x:c>
-      <x:c r="B5" s="12" t="str">
-        <x:v>Proveedores, Materias_Primas, Productos_Terminados, Recetas, Ingresos_MP, Ordenes_Produccion, Consumos_MP_OP, Ventas y Detalle_Ventas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="44" t="str">
-        <x:v>Hojas de apoyo</x:v>
-      </x:c>
-      <x:c r="B6" s="12" t="str">
-        <x:v>Guia_AppSheet, Modelo_Datos, Listas, Dashboard y Fuentes.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="44" t="str">
-        <x:v>Criterio de diseño</x:v>
-      </x:c>
-      <x:c r="B7" s="12" t="str">
-        <x:v>Modelo relacional simple, normalizado y extensible para una primera versión o MVP.</x:v>
-      </x:c>
+      <x:c r="B14" s="77" t="str">
+        <x:v>Leer el README, revisar los conceptos y el contexto, crear una copia de esta plantilla y ejecutar la guía paso a paso.</x:v>
+      </x:c>
+      <x:c r="C14" s="77"/>
+      <x:c r="D14" s="77"/>
+      <x:c r="E14" s="77"/>
+      <x:c r="F14" s="78"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="84" t="str">
+        <x:v>Datos de prueba</x:v>
+      </x:c>
+      <x:c r="B15" s="85" t="str">
+        <x:v>No utilizar datos personales, credenciales ni información productiva real durante la construcción académica.</x:v>
+      </x:c>
+      <x:c r="C15" s="85"/>
+      <x:c r="D15" s="85"/>
+      <x:c r="E15" s="85"/>
+      <x:c r="F15" s="86"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A3:A4"/>
+    <x:mergeCell ref="B3:F4"/>
+    <x:mergeCell ref="A6:F6"/>
+    <x:mergeCell ref="B7:F7"/>
+    <x:mergeCell ref="B8:F8"/>
+    <x:mergeCell ref="B9:F9"/>
+    <x:mergeCell ref="B10:F10"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:F15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -12194,7 +12812,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52cf02a2d68b47c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7479120ac7814e3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17377,7 +17995,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc49c25bae8304509"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e97e73594b4510"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22512,7 +23130,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9811e3b617314c1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R959f292f2be44b38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26718,7 +27336,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62bde60ad6b54adc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54e9602afa64885"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32820,7 +33438,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dc0231cc5d046ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bc527c6741b434f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37913,7 +38531,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31e998ee160a4061"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a64402555664480"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40989,7 +41607,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra49a1b5540be4d58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96b7b7606f84f7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45071,7 +45689,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9bdc6580b874dc5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e84b47e7e974ffa"/>
   </x:tableParts>
 </x:worksheet>
 </file>